--- a/demo/samples/sales.xlsx
+++ b/demo/samples/sales.xlsx
@@ -2,126 +2,500 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Sales" sheetId="1" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Sales" sheetId="1" r:id="r1"/>
+    <sheet name="Summary" sheetId="2" r:id="r2"/>
   </sheets>
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF174C5B"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="6">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF174C5B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F2F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE4C7"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border/>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFB4CFCB"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf/>
+  </cellStyleXfs>
+  <cellXfs count="9">
+    <xf/>
+    <xf fontId="1" fillId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="3" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1"/>
+    <xf borderId="1" fillId="4"/>
+    <xf borderId="1" numFmtId="4"/>
+    <xf borderId="1" numFmtId="10"/>
+    <xf borderId="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF8E351D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE4C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF347A78"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="DemoHeader">
+    <tableStyle name="DemoHeader" pivot="0" table="1" count="1">
+      <tableStyleElement type="headerRow" dxfId="1"/>
+    </tableStyle>
+  </tableStyles>
+</styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SalesTable" displayName="SalesTable" ref="A4:F10" headerRowCount="1">
+  <autoFilter ref="A4:F10"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Product"/>
+    <tableColumn id="2" name="Region"/>
+    <tableColumn id="3" name="Units"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Margin"/>
+    <tableColumn id="6" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="DemoHeader" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly sales overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A sample workbook with formats, tables and conditional highlights</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="23" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="33" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Notebook</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="C5" s="4">
         <v>120</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="D5" s="6">
+        <v>1860.5</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.34</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Strong spring demand across the region</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Pencil</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C6" s="5">
         <v>85</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D6" s="6">
+        <v>510.0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Restock planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="C7" s="4">
         <v>64</v>
       </c>
+      <c r="D7" s="6">
+        <v>768.25</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.28</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>New colors</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C8" s="5">
+        <v>42</v>
+      </c>
+      <c r="D8" s="6">
+        <v>252.0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Review stock levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Folders</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C9" s="4">
+        <v>96</v>
+      </c>
+      <c r="D9" s="6">
+        <v>864.0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.31</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Repeat orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Labels</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="C10" s="5">
+        <v>38</v>
+      </c>
+      <c r="D10" s="6">
+        <v>190.0</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal item</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="23" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Reading this sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="35" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Orange highlights identify low margins. Amounts and percentages use number formats.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5:E10">
+    <cfRule type="cellIs" operator="lessThan" dxfId="0">
+      <formula>0.2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <tableParts count="1">
+    <tablePart r:id="t1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Quarter</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Seasonal summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Compare seasonal totals and search across sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="23" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="23" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B5" s="4">
         <v>269</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C5" s="6">
+        <v>4444.75</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="6" ht="23" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Summer</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B6" s="5">
         <v>315</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C6" s="6">
+        <v>5132.5</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="7" ht="23" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Autumn</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B7" s="4">
         <v>288</v>
       </c>
+      <c r="C7" s="6">
+        <v>4719.25</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="8" ht="23" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Winter</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <v>240</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3920.0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.24</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
 </worksheet>
 </file>
--- a/demo/samples/sales.xlsx
+++ b/demo/samples/sales.xlsx
@@ -373,7 +373,7 @@
     <mergeCell ref="A13:F13"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E10">
-    <cfRule type="cellIs" operator="lessThan" dxfId="0">
+    <cfRule type="cellIs" operator="lessThan" dxfId="0" priority="1">
       <formula>0.2</formula>
     </cfRule>
   </conditionalFormatting>
